--- a/output/ARKF/00_Starter_Residual_over_7.5pct/ARKF_starter_residual_analysis.xlsx
+++ b/output/ARKF/00_Starter_Residual_over_7.5pct/ARKF_starter_residual_analysis.xlsx
@@ -534,7 +534,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2395</v>
+        <v>2437</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -555,10 +555,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>280</v>
+        <v>668.1</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         <v>13.84986353941615</v>
       </c>
       <c r="E2" t="n">
-        <v>3.242466314934898</v>
+        <v>3.017245113947369</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2395</v>
+        <v>2437</v>
       </c>
       <c r="H2" t="n">
-        <v>2395</v>
+        <v>2437</v>
       </c>
     </row>
   </sheetData>
@@ -658,57 +658,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bloomberg Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Transition Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Peak Weight Before %</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Weight at Transition %</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Weight Drawdown %</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Max Weight After %</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Final Weight %</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Days as Residual</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -719,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,666 +723,172 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAD Curncy</t>
+          <t>BABA US Equity</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>44111</v>
+        <v>44446</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>44235</v>
+        <v>45923</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>1477</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2632873394351858</v>
+        <v>0.5474875512866419</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>META US Equity</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43521</v>
+        <v>44558</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>43637</v>
+        <v>45281</v>
       </c>
       <c r="D4" t="n">
-        <v>116</v>
+        <v>723</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001964416139246338</v>
+        <v>0.5092618261890409</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>NVDA US Equity</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43641</v>
+        <v>44334</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>43707</v>
+        <v>44708</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>374</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3878927770042555</v>
+        <v>0.4042329336493665</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>PINS US Equity</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>43713</v>
+        <v>44545</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>43951</v>
+        <v>44952</v>
       </c>
       <c r="D6" t="n">
-        <v>238</v>
+        <v>407</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001509179929640628</v>
+        <v>0.6843959624037065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>PLTR US Equity</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>43986</v>
+        <v>44620</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>44085</v>
+        <v>45064</v>
       </c>
       <c r="D7" t="n">
-        <v>99</v>
+        <v>444</v>
       </c>
       <c r="E7" t="n">
-        <v>7.238301190557532e-07</v>
+        <v>0.2560260324007131</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>PYPL US Equity</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>44088</v>
+        <v>44610</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>44610</v>
+        <v>45436</v>
       </c>
       <c r="D8" t="n">
-        <v>522</v>
+        <v>826</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008251777708662412</v>
+        <v>0.6457146440286845</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>SE US Equity</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>44614</v>
+        <v>44881</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>45336</v>
+        <v>45356</v>
       </c>
       <c r="D9" t="n">
-        <v>722</v>
+        <v>475</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1612095762656547</v>
+        <v>0.2505158017269435</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>SHOP CN Equity</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45337</v>
+        <v>43900</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>45385</v>
+        <v>44132</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0001897852011505419</v>
+        <v>0.4834538818653537</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HKD Curncy</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>44032</v>
+        <v>43773</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>44172</v>
+        <v>44531</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>758</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06757609380609853</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>HKD Curncy</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>44372</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>44442</v>
-      </c>
-      <c r="D12" t="n">
-        <v>70</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.2130721935694165</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HKD Curncy</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>44446</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>45385</v>
-      </c>
-      <c r="D13" t="n">
-        <v>939</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-5.06221859042014e-07</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>43675</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>43810</v>
-      </c>
-      <c r="D14" t="n">
-        <v>135</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.0142690742599815</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>43811</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>43894</v>
-      </c>
-      <c r="D15" t="n">
-        <v>83</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.011516593765187</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>43906</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>43971</v>
-      </c>
-      <c r="D16" t="n">
-        <v>65</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.09051575473033632</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>43991</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>44025</v>
-      </c>
-      <c r="D17" t="n">
-        <v>34</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.05187143232492531</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>44026</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>44067</v>
-      </c>
-      <c r="D18" t="n">
-        <v>41</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.07743346053086182</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>44225</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>44266</v>
-      </c>
-      <c r="D19" t="n">
-        <v>41</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.01131133997354291</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>44298</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>44342</v>
-      </c>
-      <c r="D20" t="n">
-        <v>44</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.1330329822073394</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>44364</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>44610</v>
-      </c>
-      <c r="D21" t="n">
-        <v>246</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.002443742261310396</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>44630</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>44690</v>
-      </c>
-      <c r="D22" t="n">
-        <v>60</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.003012984095514021</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>44728</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>44778</v>
-      </c>
-      <c r="D23" t="n">
-        <v>50</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.001416672609090148</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>44781</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>44957</v>
-      </c>
-      <c r="D24" t="n">
-        <v>176</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.008081244977611568</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>44958</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>45079</v>
-      </c>
-      <c r="D25" t="n">
-        <v>121</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.01569686210095401</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45082</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>45282</v>
-      </c>
-      <c r="D26" t="n">
-        <v>200</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.2239422313308192</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45286</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>45357</v>
-      </c>
-      <c r="D27" t="n">
-        <v>71</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.5111178541361689</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>META US Equity</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>44558</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>45281</v>
-      </c>
-      <c r="D28" t="n">
-        <v>723</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.5092618261890409</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>NVDA US Equity</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>44334</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>44708</v>
-      </c>
-      <c r="D29" t="n">
-        <v>374</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.4042329336493665</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PINS US Equity</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>44545</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>44952</v>
-      </c>
-      <c r="D30" t="n">
-        <v>407</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.6843959624037065</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PLTR US Equity</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>44620</v>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>45064</v>
-      </c>
-      <c r="D31" t="n">
-        <v>444</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.2560260324007131</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>PYPL US Equity</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>44610</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>45436</v>
-      </c>
-      <c r="D32" t="n">
-        <v>826</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.6457146440286845</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>SE US Equity</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>44881</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>45356</v>
-      </c>
-      <c r="D33" t="n">
-        <v>475</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.2505158017269435</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>SHOP CN Equity</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>43900</v>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>44132</v>
-      </c>
-      <c r="D34" t="n">
-        <v>232</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.4834538818653537</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TWTR US Equity</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>43773</v>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>44531</v>
-      </c>
-      <c r="D35" t="n">
-        <v>758</v>
-      </c>
-      <c r="E35" t="n">
         <v>0.5063608440363557</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ZAR Curncy</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>44959</v>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>45215</v>
-      </c>
-      <c r="D36" t="n">
-        <v>256</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02232509365285203</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ZAR Curncy</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45216</v>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>45385</v>
-      </c>
-      <c r="D37" t="n">
-        <v>169</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-0.0003329798795747985</v>
       </c>
     </row>
   </sheetData>
